--- a/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_67606_completo.xlsx
+++ b/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_67606_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2991dfd835764c52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R23e18db4d1554a21"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1690</x:v>
+        <x:v>      0.1694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1690</x:v>
+        <x:v>      0.1694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1690</x:v>
+        <x:v>      0.1694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1690</x:v>
+        <x:v>      0.1694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2167</x:v>
+        <x:v>      0.2157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6778</x:v>
+        <x:v>      0.6715</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4528</x:v>
+        <x:v>      0.4479</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4528</x:v>
+        <x:v>      0.4479</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5233</x:v>
+        <x:v>      0.5178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6778</x:v>
+        <x:v>      0.6715</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6778</x:v>
+        <x:v>      0.6715</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.7619</x:v>
+        <x:v>      0.7554</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3256</x:v>
+        <x:v>      0.3224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2689</x:v>
+        <x:v>      0.2667</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3870</x:v>
+        <x:v>      0.3828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5233</x:v>
+        <x:v>      0.5178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5233</x:v>
+        <x:v>      0.5178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5233</x:v>
+        <x:v>      0.5178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5233</x:v>
+        <x:v>      0.5178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5233</x:v>
+        <x:v>      0.5178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5982</x:v>
+        <x:v>      0.5923</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6778</x:v>
+        <x:v>      0.6715</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.7619</x:v>
+        <x:v>      0.7554</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.8505</x:v>
+        <x:v>      0.8441</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0415</x:v>
+        <x:v>      1.0354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0415</x:v>
+        <x:v>      1.0354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2506</x:v>
+        <x:v>      1.2456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3621</x:v>
+        <x:v>      1.3577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3621</x:v>
+        <x:v>      1.3577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0415</x:v>
+        <x:v>      1.0354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2506</x:v>
+        <x:v>      1.2456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3621</x:v>
+        <x:v>      1.3577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4780</x:v>
+        <x:v>      1.4746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4780</x:v>
+        <x:v>      1.4746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4780</x:v>
+        <x:v>      1.4746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4780</x:v>
+        <x:v>      1.4746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4780</x:v>
+        <x:v>      1.4746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.4780</x:v>
+        <x:v>      1.4746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2506</x:v>
+        <x:v>      1.2456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2506</x:v>
+        <x:v>      1.2456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.2506</x:v>
+        <x:v>      1.2456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.9437</x:v>
+        <x:v>      0.9374</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.0415</x:v>
+        <x:v>      1.0354</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.3621</x:v>
+        <x:v>      1.3577</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9875</x:v>
+        <x:v>      1.9890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2695</x:v>
+        <x:v>      2.2744</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9875</x:v>
+        <x:v>      1.9890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9875</x:v>
+        <x:v>      1.9890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2695</x:v>
+        <x:v>      2.2744</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.7236</x:v>
+        <x:v>      1.7224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9875</x:v>
+        <x:v>      1.9890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.1262</x:v>
+        <x:v>      2.1293</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2695</x:v>
+        <x:v>      2.2744</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2695</x:v>
+        <x:v>      2.2744</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3609,7 +3744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.2695</x:v>
+        <x:v>      2.2744</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3639,7 +3774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9875</x:v>
+        <x:v>      1.9890</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_67606_completo.xlsx
+++ b/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_67606_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R23e18db4d1554a21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1627b199f9734fe4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2744</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3828</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1694</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3828</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6715</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
